--- a/public/plantillas/Template_Carga_Masiva_PEI.xlsx
+++ b/public/plantillas/Template_Carga_Masiva_PEI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\FrontendGoreSM\frontend-dashboardgoresm\public\plantillas\Plantillas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\CargaMasiva\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C536C8-2F17-4E2C-8D7E-E7C069527103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8E2609-EA5E-48C5-A980-DE9284BD9AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_PEI_INDICADOR_VALOR" sheetId="1" r:id="rId1"/>
@@ -381,7 +381,7 @@
     <t>Indicador estratégico institucional</t>
   </si>
   <si>
-    <t>[2019 - 2026]</t>
+    <t>2023 - 2026</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +1121,7 @@
       <formula1>"VALOR"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="S2" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"Meta,Linea de base"</formula1>
+      <formula1>"Meta,Línea de base"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
